--- a/VBX_Command_Center_v1.xlsx
+++ b/VBX_Command_Center_v1.xlsx
@@ -2410,7 +2410,7 @@
     <row r="12" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C12" s="11" t="n">
         <f aca="false">SUMPRODUCT((Pipeline!E5:E1000&lt;&gt;"")*(Pipeline!E5:E1000&lt;&gt;"Awarded")*(Pipeline!E5:E1000&lt;&gt;"Lost"))</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D12" s="8" t="n">
         <f aca="false">SUMIFS(Pipeline!F5:F1000,Pipeline!E5:E1000,"&lt;&gt;Awarded",Pipeline!E5:E1000,"&lt;&gt;Lost",Pipeline!E5:E1000,"&lt;&gt;")</f>
@@ -18303,40 +18303,142 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="42"/>
-      <c r="B10" s="42"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="43"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="41"/>
-      <c r="I10" s="42"/>
-      <c r="J10" s="42"/>
+      <c r="A10" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPP-006</t>
+        </is>
+      </c>
+      <c r="B10" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CBO "SENTRY" IT Engineering Support (CB26-RFQ0012)</t>
+        </is>
+      </c>
+      <c r="C10" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Congressional Budget Office (CBO)</t>
+        </is>
+      </c>
+      <c r="D10" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">541519</t>
+        </is>
+      </c>
+      <c r="E10" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Capture</t>
+        </is>
+      </c>
+      <c r="F10" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="41" t="n">
+        <v>46175</v>
+      </c>
+      <c r="H10" s="41" t="n">
+        <v>46178</v>
+      </c>
+      <c r="I10" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Khaalis Wooden</t>
+        </is>
+      </c>
+      <c r="J10" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Teaming with The Enterprise Solutions (TES). Network/DevSecOps/Service Desk/Web Security/Cybersecurity DoWs (J2,J3,J6-J9). 12-mo base + 4 option yrs. Value TBD.</t>
+        </is>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="42"/>
-      <c r="B11" s="42"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="43"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="41"/>
-      <c r="I11" s="42"/>
-      <c r="J11" s="42"/>
+      <c r="A11" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPP-007</t>
+        </is>
+      </c>
+      <c r="B11" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CDC IFMS Services &amp; Support (75D301-26-Q-78924)</t>
+        </is>
+      </c>
+      <c r="C11" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Centers for Disease Control and Prevention (CDC)</t>
+        </is>
+      </c>
+      <c r="D11" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">541512</t>
+        </is>
+      </c>
+      <c r="E11" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Capture</t>
+        </is>
+      </c>
+      <c r="F11" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="41" t="n">
+        <v>46175</v>
+      </c>
+      <c r="H11" s="41" t="n">
+        <v>46178</v>
+      </c>
+      <c r="I11" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Khaalis Wooden</t>
+        </is>
+      </c>
+      <c r="J11" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Teaming with The Enterprise Solutions (TES). NAICS 541512, GSA SIN 54151S, 100% small business set-aside. Base + 4 option yrs (PoP 7/1/2026). Value TBD.</t>
+        </is>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="42"/>
-      <c r="B12" s="42"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="41"/>
-      <c r="I12" s="42"/>
-      <c r="J12" s="42"/>
+      <c r="A12" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPP-008</t>
+        </is>
+      </c>
+      <c r="B12" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VA TERPS Support (36C10B26Q0107)</t>
+        </is>
+      </c>
+      <c r="C12" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Veterans Affairs (VA)</t>
+        </is>
+      </c>
+      <c r="D12" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">541512</t>
+        </is>
+      </c>
+      <c r="E12" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Capture</t>
+        </is>
+      </c>
+      <c r="F12" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="41" t="n">
+        <v>46175</v>
+      </c>
+      <c r="H12" s="41" t="n">
+        <v>46178</v>
+      </c>
+      <c r="I12" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Khaalis Wooden</t>
+        </is>
+      </c>
+      <c r="J12" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Teaming with The Enterprise Solutions (TES). TERPS PWS. NOTE: uploaded PDF body mislabeled vs filename - verify PWS scope. NAICS/value TBD.</t>
+        </is>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="42"/>

--- a/VBX_Command_Center_v1.xlsx
+++ b/VBX_Command_Center_v1.xlsx
@@ -2414,7 +2414,7 @@
       </c>
       <c r="D12" s="8" t="n">
         <f aca="false">SUMIFS(Pipeline!F5:F1000,Pipeline!E5:E1000,"&lt;&gt;Awarded",Pipeline!E5:E1000,"&lt;&gt;Lost",Pipeline!E5:E1000,"&lt;&gt;")</f>
-        <v>14500000</v>
+        <v>69000000</v>
       </c>
       <c r="E12" s="11" t="n">
         <f aca="false">COUNTIFS(Active_Projects!H:H,"Active")</f>
@@ -18329,7 +18329,7 @@
         </is>
       </c>
       <c r="F10" s="43" t="n">
-        <v>0</v>
+        <v>30000000</v>
       </c>
       <c r="G10" s="41" t="n">
         <v>46175</v>
@@ -18344,7 +18344,7 @@
       </c>
       <c r="J10" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Teaming with The Enterprise Solutions (TES). Network/DevSecOps/Service Desk/Web Security/Cybersecurity DoWs (J2,J3,J6-J9). 12-mo base + 4 option yrs. Value TBD.</t>
+          <t xml:space="preserve">Teaming with The Enterprise Solutions (TES). Network/DevSecOps/Service Desk/Web Security/Cybersecurity DoWs (J2,J3,J6-J9). 12-mo base + 4 option yrs. Est. $30M point (range $20-50M BPA ceiling; comparable-award basis, Medium-Low confidence). Capture verdict: CONDITIONAL.</t>
         </is>
       </c>
     </row>
@@ -18375,7 +18375,7 @@
         </is>
       </c>
       <c r="F11" s="43" t="n">
-        <v>0</v>
+        <v>4500000</v>
       </c>
       <c r="G11" s="41" t="n">
         <v>46175</v>
@@ -18390,7 +18390,7 @@
       </c>
       <c r="J11" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Teaming with The Enterprise Solutions (TES). NAICS 541512, GSA SIN 54151S, 100% small business set-aside. Base + 4 option yrs (PoP 7/1/2026). Value TBD.</t>
+          <t xml:space="preserve">Teaming with The Enterprise Solutions (TES). NAICS 541512, GSA SIN 54151S, 100% small business set-aside. Base + 4 option yrs (PoP 7/1/2026). Est. $4.5M point (range $3-6M; TRIRIGA comparable basis, Medium confidence). Capture verdict: NO-BID (COTS/reseller policy).</t>
         </is>
       </c>
     </row>
@@ -18421,7 +18421,7 @@
         </is>
       </c>
       <c r="F12" s="43" t="n">
-        <v>0</v>
+        <v>20000000</v>
       </c>
       <c r="G12" s="41" t="n">
         <v>46175</v>
@@ -18436,7 +18436,7 @@
       </c>
       <c r="J12" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Teaming with The Enterprise Solutions (TES). TERPS PWS. NOTE: uploaded PDF body mislabeled vs filename - verify PWS scope. NAICS/value TBD.</t>
+          <t xml:space="preserve">Teaming with The Enterprise Solutions (TES). Sol. 36C10B26Q0107 = VA VIPPS (Phase II) per capture analysis - title TERPS is a mislabel to correct. Est. $20M point (range $15-40M, Medium confidence). Capture verdict: PURSUE - Flagship.</t>
         </is>
       </c>
     </row>

--- a/VBX_Command_Center_v1.xlsx
+++ b/VBX_Command_Center_v1.xlsx
@@ -18402,7 +18402,7 @@
       </c>
       <c r="B12" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">VA TERPS Support (36C10B26Q0107)</t>
+          <t xml:space="preserve">VA VIPPS (Phase II) - VistA/iFAMS Integration (36C10B26Q0107)</t>
         </is>
       </c>
       <c r="C12" s="42" t="inlineStr">
@@ -18436,7 +18436,7 @@
       </c>
       <c r="J12" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Teaming with The Enterprise Solutions (TES). Sol. 36C10B26Q0107 = VA VIPPS (Phase II) per capture analysis - title TERPS is a mislabel to correct. Est. $20M point (range $15-40M, Medium confidence). Capture verdict: PURSUE - Flagship.</t>
+          <t xml:space="preserve">Teaming with The Enterprise Solutions (TES). VA OIT; GSA MAS / SIN 54151S. Phase II only (Phase I closed 5/4/26). Best Value Trade-Off, FFP; PoP 12-mo base + 4 option yrs (close 7/1/2026). Scope: VistA / iFAMS / FORCE integration + AI/ML + FedRAMP Mod + RMF. Est. $20M point (range $15-40M; most likely $15-25M, Medium confidence). FLAGSHIP - PURSUE.</t>
         </is>
       </c>
     </row>

--- a/VBX_Command_Center_v1.xlsx
+++ b/VBX_Command_Center_v1.xlsx
@@ -2409,12 +2409,12 @@
     </row>
     <row r="12" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C12" s="11" t="n">
-        <f aca="false">SUMPRODUCT((Pipeline!E5:E1000&lt;&gt;"")*(Pipeline!E5:E1000&lt;&gt;"Awarded")*(Pipeline!E5:E1000&lt;&gt;"Lost"))</f>
-        <v>8</v>
+        <f aca="false">SUMPRODUCT((Pipeline!E5:E1000&lt;&gt;"")*(Pipeline!E5:E1000&lt;&gt;"Awarded")*(Pipeline!E5:E1000&lt;&gt;"Lost")*(Pipeline!E5:E1000&lt;&gt;"No-Bid"))</f>
+        <v>12</v>
       </c>
       <c r="D12" s="8" t="n">
-        <f aca="false">SUMIFS(Pipeline!F5:F1000,Pipeline!E5:E1000,"&lt;&gt;Awarded",Pipeline!E5:E1000,"&lt;&gt;Lost",Pipeline!E5:E1000,"&lt;&gt;")</f>
-        <v>69000000</v>
+        <f aca="false">SUMIFS(Pipeline!F5:F1000,Pipeline!E5:E1000,"&lt;&gt;Awarded",Pipeline!E5:E1000,"&lt;&gt;Lost",Pipeline!E5:E1000,"&lt;&gt;",Pipeline!E5:E1000,"&lt;&gt;No-Bid")</f>
+        <v>118500000</v>
       </c>
       <c r="E12" s="11" t="n">
         <f aca="false">COUNTIFS(Active_Projects!H:H,"Active")</f>
@@ -18371,7 +18371,7 @@
       </c>
       <c r="E11" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Capture</t>
+          <t xml:space="preserve">No-Bid</t>
         </is>
       </c>
       <c r="F11" s="43" t="n">
@@ -18436,69 +18436,239 @@
       </c>
       <c r="J12" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Teaming with The Enterprise Solutions (TES). VA OIT; GSA MAS / SIN 54151S. Phase II only (Phase I closed 5/4/26). Best Value Trade-Off, FFP; PoP 12-mo base + 4 option yrs (close 7/1/2026). Scope: VistA / iFAMS / FORCE integration + AI/ML + FedRAMP Mod + RMF. Est. $20M point (range $15-40M; most likely $15-25M, Medium confidence). FLAGSHIP - PURSUE.</t>
+          <t xml:space="preserve">Teaming with The Enterprise Solutions (TES). VA OIT; GSA MAS / SIN 54151S. Phase II only (Phase I closed 5/4/26). Best Value Trade-Off, FFP; PoP 12-mo base + 4 option yrs (close 7/1/2026). Scope: VistA / iFAMS / FORCE integration + AI/ML + FedRAMP Mod + RMF. Est. $20M point (range $15-40M; most likely $15-25M, Medium confidence). FLAGSHIP - PURSUE. Confirm TES Phase I submission before further work.</t>
         </is>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="42"/>
-      <c r="B13" s="42"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="41"/>
-      <c r="I13" s="42"/>
-      <c r="J13" s="42"/>
+      <c r="A13" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPP-009</t>
+        </is>
+      </c>
+      <c r="B13" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPM OIG BRIDGE BPA - FEHBP Claims Data Governance (eBuy)</t>
+        </is>
+      </c>
+      <c r="C13" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPM Office of Inspector General</t>
+        </is>
+      </c>
+      <c r="D13" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">541512</t>
+        </is>
+      </c>
+      <c r="E13" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Capture</t>
+        </is>
+      </c>
+      <c r="F13" s="43" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="G13" s="41" t="n">
+        <v>46176</v>
+      </c>
+      <c r="H13" s="41" t="n">
+        <v>46178</v>
+      </c>
+      <c r="I13" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Khaalis Wooden</t>
+        </is>
+      </c>
+      <c r="J13" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Teaming with TES (8(a) prime; VBX sub ~40-45% on data engineering + AI/ML). BRIDGE = Benefits &amp; Retirement Integrated Data Governance Environment - OPM OIG FEHBP claims warehouse. INCUMBENT: Unissant (since 2018, 8(a)) - strong threat. RISK: TES 8(a) runway (yr 7-8 of 9) - verify cert through 9/27 option period. Differentiator: VBX commercial claims-at-scale PP federalized. 5-yr BPA, close 6/12/26. Est. $15M (range $8-25M, Medium). Verdict: PURSUE - PRIORITY. [NAICS inferred - verify]</t>
+        </is>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="42"/>
-      <c r="B14" s="42"/>
-      <c r="C14" s="42"/>
-      <c r="D14" s="42"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="41"/>
-      <c r="H14" s="41"/>
-      <c r="I14" s="42"/>
-      <c r="J14" s="42"/>
+      <c r="A14" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPP-010</t>
+        </is>
+      </c>
+      <c r="B14" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NIH Data Access &amp; Data Linkage BPA (75N98026Q00309)</t>
+        </is>
+      </c>
+      <c r="C14" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NIH / HHS</t>
+        </is>
+      </c>
+      <c r="D14" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">541512</t>
+        </is>
+      </c>
+      <c r="E14" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Capture</t>
+        </is>
+      </c>
+      <c r="F14" s="43" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="G14" s="41" t="n">
+        <v>46176</v>
+      </c>
+      <c r="H14" s="41" t="n">
+        <v>46178</v>
+      </c>
+      <c r="I14" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Khaalis Wooden</t>
+        </is>
+      </c>
+      <c r="J14" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Teaming with TES. NIA LINKAGE - federated research data enclave (NIH studies linked to CMS data). 3 CORFPs (multi-cloud data / data linkage / tech support; multi-award likely). Reqs: FISMA Mod + Zero Trust + IAL2 + ConMon. INCUMBENT: likely Lifebit or BAH/Leidos NIH shops. RISKS: no NIH research-enclave PP (verify TES); federated multi-cloud is a specialization gap; set-aside unconfirmed. Consider sub-only via Lifebit/BAH if priming gates too high. Close 6/18/26. Est. $25M (range $10-50M, Medium). Verdict: PURSUE - eyes open. [NAICS inferred - verify]</t>
+        </is>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="42"/>
-      <c r="B15" s="42"/>
-      <c r="C15" s="42"/>
-      <c r="D15" s="42"/>
-      <c r="E15" s="42"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="41"/>
-      <c r="I15" s="42"/>
-      <c r="J15" s="42"/>
+      <c r="A15" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPP-011</t>
+        </is>
+      </c>
+      <c r="B15" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kuali Coeus Support Services (N00244-26-Q-0016)</t>
+        </is>
+      </c>
+      <c r="C15" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Navy - Naval Postgraduate School</t>
+        </is>
+      </c>
+      <c r="D15" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">541511</t>
+        </is>
+      </c>
+      <c r="E15" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qualified</t>
+        </is>
+      </c>
+      <c r="F15" s="43" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="G15" s="41" t="n">
+        <v>46176</v>
+      </c>
+      <c r="H15" s="41" t="n">
+        <v>46178</v>
+      </c>
+      <c r="I15" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Khaalis Wooden</t>
+        </is>
+      </c>
+      <c r="J15" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Teaming with TES (WOSB set-aside = TES qualifies). Java developer support to customize Kuali Coeus (research admin system) at NPS. GSA MAS/54151S, 12-mo base + 4 option yrs. Smaller scope; pursue only if VIPPS triage gives bandwidth. Close 6/8/26. Est. $4M (range $2-8M, Medium-Low). Verdict: PURSUE IF CAPACITY. [NAICS inferred - verify]</t>
+        </is>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="42"/>
-      <c r="B16" s="42"/>
-      <c r="C16" s="42"/>
-      <c r="D16" s="42"/>
-      <c r="E16" s="42"/>
-      <c r="F16" s="43"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="41"/>
-      <c r="I16" s="42"/>
-      <c r="J16" s="42"/>
+      <c r="A16" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPP-012</t>
+        </is>
+      </c>
+      <c r="B16" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FTC Infrastructure Mgmt Support / IMSS (29FTC126R0001)</t>
+        </is>
+      </c>
+      <c r="C16" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Federal Trade Commission (FTC)</t>
+        </is>
+      </c>
+      <c r="D16" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">541519</t>
+        </is>
+      </c>
+      <c r="E16" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Identified</t>
+        </is>
+      </c>
+      <c r="F16" s="43" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="G16" s="41" t="n">
+        <v>46176</v>
+      </c>
+      <c r="H16" s="41" t="n">
+        <v>46178</v>
+      </c>
+      <c r="I16" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Khaalis Wooden</t>
+        </is>
+      </c>
+      <c r="J16" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Teaming with TES. FTC IT infrastructure architecture, O&amp;M, config mgmt, ad-hoc IT. Small agency, no healthcare angle. Pursue only with FTC relationship lift. Set-aside open/TBD. Close 6/12/26. Est. $5M (range $3-10M, Medium-Low). Verdict: CONSIDER. [NAICS inferred - verify]</t>
+        </is>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="42"/>
-      <c r="B17" s="42"/>
-      <c r="C17" s="42"/>
-      <c r="D17" s="42"/>
-      <c r="E17" s="42"/>
-      <c r="F17" s="43"/>
-      <c r="G17" s="41"/>
-      <c r="H17" s="41"/>
-      <c r="I17" s="42"/>
-      <c r="J17" s="42"/>
+      <c r="A17" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPP-013</t>
+        </is>
+      </c>
+      <c r="B17" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPM OIG Investigative Tracking System (eBuy)</t>
+        </is>
+      </c>
+      <c r="C17" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPM Office of Inspector General</t>
+        </is>
+      </c>
+      <c r="D17" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">541511</t>
+        </is>
+      </c>
+      <c r="E17" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Identified</t>
+        </is>
+      </c>
+      <c r="F17" s="43" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="G17" s="41" t="n">
+        <v>46176</v>
+      </c>
+      <c r="H17" s="41" t="n">
+        <v>46178</v>
+      </c>
+      <c r="I17" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Khaalis Wooden</t>
+        </is>
+      </c>
+      <c r="J17" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Teaming with TES. OPM OIG Office of Investigations case management (intake -&gt; assignment -&gt; evidence -&gt; reporting -&gt; CIGIE compliance). Distinct from audit-side ETS (TSPi/Salesforce). KEY RISK: TSPi pitches ETS extension. Competitors: Casepoint eCASE, Secure Case Mgmt, 8(a) custom-dev. Down-select = higher proposal cost. Action: verify set-aside; probe sub-prime w/ Casepoint or Secure CMS. 5-yr (9/30/26-9/29/31). Est. $5M (range $3-10M, Medium). Verdict: CONSIDER - verify set-aside. [NAICS inferred - verify]</t>
+        </is>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="42"/>
